--- a/02_DIA_inicio_2026_analisis_assets/rbd_9458_escuela-boroa_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9458_escuela-boroa_nt2_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3F8F886-716A-43D1-8209-0D24A6569190}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8300B186-8133-4887-9D90-2F6E2913FD9B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C990EE3B-BCFC-4621-87DA-49DE805DA0BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49EDC7BA-5327-4CB6-976A-DF063607CECA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F110BBE4-52B6-4F78-B371-4D93C6C0288C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7087A79-C0F9-4ECE-8FAC-93701667C8E8}"/>
 </file>